--- a/EPIC_0008_Referal_Management.xlsx
+++ b/EPIC_0008_Referal_Management.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3A8052-1ED3-4C96-8349-5ACCE99F805C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3681551B-053E-404D-B800-4FD09714C74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -316,10 +316,10 @@
     <t>Referal Mangement</t>
   </si>
   <si>
-    <t>TC_RG_01_Referal Mangagement</t>
-  </si>
-  <si>
     <t>This end-to-end hybrid regression test verifies the referal management test Flow</t>
+  </si>
+  <si>
+    <t>TC_RG_02_Referal Mangagement</t>
   </si>
 </sst>
 </file>
@@ -821,10 +821,10 @@
         <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
